--- a/static/report/transport.xlsx
+++ b/static/report/transport.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repo\phoenix12\static\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869FEF1D-23F9-41F6-AA8D-FF0CB161B4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945E8501-CB8F-4E02-B168-A9BF4D30C0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8928" activeTab="2" xr2:uid="{61C94974-93D3-4F6B-905C-DE951FBA0ECE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{61C94974-93D3-4F6B-905C-DE951FBA0ECE}"/>
   </bookViews>
   <sheets>
     <sheet name="vehicles" sheetId="1" r:id="rId1"/>
     <sheet name="oil_details" sheetId="2" r:id="rId2"/>
     <sheet name="OilingMaintenanceDetails" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,12 +29,14 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -401,7 +402,8 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="9.109375" style="1"/>
+    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.109375" style="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -424,13 +426,4 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589249CD-80E4-43AE-8B2F-DAB64246AF5D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/static/report/transport.xlsx
+++ b/static/report/transport.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repo\phoenix12\static\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945E8501-CB8F-4E02-B168-A9BF4D30C0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D83ED4-2322-43CD-8C08-2ED63E077DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{61C94974-93D3-4F6B-905C-DE951FBA0ECE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{61C94974-93D3-4F6B-905C-DE951FBA0ECE}"/>
   </bookViews>
   <sheets>
     <sheet name="vehicles" sheetId="1" r:id="rId1"/>
-    <sheet name="oil_details" sheetId="2" r:id="rId2"/>
-    <sheet name="OilingMaintenanceDetails" sheetId="3" r:id="rId3"/>
+    <sheet name="drivers" sheetId="4" r:id="rId2"/>
+    <sheet name="statuses" sheetId="5" r:id="rId3"/>
+    <sheet name="oil_details" sheetId="2" r:id="rId4"/>
+    <sheet name="OilingMaintenanceDetails" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,10 +35,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -400,10 +398,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{276EF5DE-7141-4AF4-9506-6E1A774177DF}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="9.109375" style="1"/>
+    <col min="1" max="1" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="9.140625" style="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -411,18 +409,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667613A8-2DC9-4E23-8256-335FB00415BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E9F016-3CDC-481C-8758-E8355B5339B6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C4C98A-069D-429A-A640-95F0EECE256C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667613A8-2DC9-4E23-8256-335FB00415BB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE05CE55-9B7F-4B9A-BFE3-6D7741EE59F4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/static/report/transport.xlsx
+++ b/static/report/transport.xlsx
@@ -5,19 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repo\phoenix12\static\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\public_html\phoenix12\static\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D83ED4-2322-43CD-8C08-2ED63E077DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD533043-A7B6-4CF5-9BA8-8F459B7437E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{61C94974-93D3-4F6B-905C-DE951FBA0ECE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{61C94974-93D3-4F6B-905C-DE951FBA0ECE}"/>
   </bookViews>
   <sheets>
-    <sheet name="vehicles" sheetId="1" r:id="rId1"/>
-    <sheet name="drivers" sheetId="4" r:id="rId2"/>
-    <sheet name="statuses" sheetId="5" r:id="rId3"/>
-    <sheet name="oil_details" sheetId="2" r:id="rId4"/>
-    <sheet name="OilingMaintenanceDetails" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,17 +35,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,16 +61,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -396,49 +379,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{276EF5DE-7141-4AF4-9506-6E1A774177DF}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="9.140625" style="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E9F016-3CDC-481C-8758-E8355B5339B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43B6190-8470-465F-973E-97D65EE72769}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C4C98A-069D-429A-A640-95F0EECE256C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667613A8-2DC9-4E23-8256-335FB00415BB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE05CE55-9B7F-4B9A-BFE3-6D7741EE59F4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
